--- a/output/2026-09-20_23_Croazia_Istarska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_23_Croazia_Istarska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centro autorizzato Kärcher - vendita e assistenza aspiratori industriali wet&amp;dry e macchine di pulizia professionale. Esistenza e contatti confermati tramite sito ufficiale Kärcher e sito Debenc (ricerca web: kaercher.com, debenc.hr, companywall.hr). Presente anche centro gemello a Rijeka, fuori contea, non incluso.</t>
+          <t>Centro autorizzato Kärcher - vendita e assistenza aspiratori industriali wet&amp;dry e macchine di pulizia professionale. Esistenza e contatti confermati tramite sito ufficiale Kärcher e sito Debenc (ricerca web: kaercher.com, debenc.hr, companywall.hr). Presente anche centro gemello a Rijeka, fuori contea, non incluso. [DUPLICATO — vedi anche: 2026-09-20_17_Croazia_Istarska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rivenditore e centro assistenza autorizzato Nilfisk-Alto - vendita idropulitrici e aspiratori industriali (incl. modello ATTIX 50). Esistenza confermata tramite registri camerali (mojkvart.hr, poslovna.hr, tvrtke.hr) e sito ufficiale oso.com.hr.</t>
+          <t>Rivenditore e centro assistenza autorizzato Nilfisk-Alto - vendita idropulitrici e aspiratori industriali (incl. modello ATTIX 50). Esistenza confermata tramite registri camerali (mojkvart.hr, poslovna.hr, tvrtke.hr) e sito ufficiale oso.com.hr. [DUPLICATO — vedi anche: 2026-09-20_17_Croazia_Istarska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -582,10 +582,9 @@
           <t>052 663 102</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Željezarija/ferramenta industriale attiva dal 1992 (OIB 73814464579) - vendita macchine e attrezzature, utensili da taglio, materiale per saldatura/molatura, materiale edile. Confermata su registri camerali (fininfo.hr, tvrtke.hr, poslovni.buzet.hr). Non specializzata in aspirazione industriale, ma canale B2B di vendita macchine/attrezzature coerente col target metalworking.</t>
+          <t>Željezarija/ferramenta industriale attiva dal 1992 (OIB 73814464579) - vendita macchine e attrezzature, utensili da taglio, materiale per saldatura/molatura, materiale edile. Confermata su registri camerali (fininfo.hr, tvrtke.hr, poslovni.buzet.hr). Non specializzata in aspirazione industriale, ma canale B2B di vendita macchine/attrezzature coerente col target metalworking. [DUPLICATO — vedi anche: 2026-09-20_22_Croazia_Istarska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-09-20_23_Croazia_Istarska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_23_Croazia_Istarska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-20_23_Croazia_Istarska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_23_Croazia_Istarska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore multinazionale di utensili, ferramenta e forniture industriali per officine/metalworking. Filiale e contatti confermati sul sito ufficiale Würth Hrvatska. Non specializzato in aspirazione industriale ma rilevante canale B2B generalista per il settore metalworking.</t>
+          <t>Distributore multinazionale di utensili, ferramenta e forniture industriali per officine/metalworking. Filiale e contatti confermati sul sito ufficiale Würth Hrvatska. Non specializzato in aspirazione industriale ma rilevante canale B2B generalista per il settore metalworking. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
